--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -700,7 +700,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683870.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>1.01Y</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/1.4800</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -907,7 +911,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
@@ -920,7 +926,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>012682372.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.38Y</t>
@@ -1140,7 +1150,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102683872.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>5+5</t>
@@ -1179,7 +1193,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1360,7 +1374,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>102683867.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -1399,7 +1417,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/1.6000</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1582,7 +1600,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>012682376.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -1802,7 +1824,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102683864.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>5+5</t>
@@ -1841,7 +1867,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2022,7 +2048,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>102683865.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2242,7 +2272,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683866.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2462,7 +2496,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>012682375.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -2682,7 +2720,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102683871.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2721,7 +2763,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/1.7200</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2889,7 +2931,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -3173,7 +3217,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3605,7 +3649,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3773,7 +3817,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
@@ -3825,7 +3871,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3993,7 +4039,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
@@ -4049,7 +4097,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -4495,7 +4543,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4663,7 +4711,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
@@ -4721,7 +4771,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -4889,7 +4939,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -4945,7 +4997,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5177,7 +5229,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9500</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5362,7 +5414,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>012682373.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>0.25Y</t>
@@ -5401,7 +5457,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4900/1.4400</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5569,7 +5625,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -5582,7 +5640,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>102683869.IB</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -5621,7 +5683,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>1.6600/1.6100</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5793,7 +5855,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ25" s="3"/>
+      <c r="AZ25" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -5806,7 +5870,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>102683868.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -6026,7 +6094,11 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>012682374.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t>0.12Y</t>
@@ -6065,7 +6137,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6237,7 +6309,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -6293,7 +6367,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6513,7 +6587,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-08" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-09" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-08</t>
+          <t>数据来源：DM    2026-10-09</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
@@ -753,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 17.30</t>
+          <t>C- 19.30</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -768,7 +770,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -776,8 +778,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.23</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -939,7 +945,9 @@
       <c r="E4" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
@@ -979,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 27.82</t>
+          <t>C 27.99</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1002,8 +1010,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -1163,7 +1175,9 @@
       <c r="E5" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -1203,7 +1217,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 37.32</t>
+          <t>B- 37.83</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1218,7 +1232,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1226,8 +1240,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -1387,7 +1405,9 @@
       <c r="E6" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>9.5</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.90</t>
@@ -1417,7 +1437,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6200/1.6000</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1427,7 +1447,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.44</t>
+          <t>C- 10.73</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1442,7 +1462,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1450,8 +1470,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>2.06</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1613,7 +1637,9 @@
       <c r="E7" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
@@ -1668,7 +1694,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1676,8 +1702,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t>4-</t>
@@ -1837,7 +1867,9 @@
       <c r="E8" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -1877,7 +1909,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 37.32</t>
+          <t>B- 37.83</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1892,7 +1924,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1900,8 +1932,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -2061,7 +2097,9 @@
       <c r="E9" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.90</t>
@@ -2101,7 +2139,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>C- 14.84</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2116,7 +2154,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2124,8 +2162,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -2285,7 +2327,9 @@
       <c r="E10" s="4" t="n">
         <v>3.6</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="n">
+        <v>3.6</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.90</t>
@@ -2325,7 +2369,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>C- 14.84</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2340,7 +2384,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2348,8 +2392,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -2509,7 +2557,9 @@
       <c r="E11" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.60</t>
@@ -2534,7 +2584,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5022</t>
+          <t>1.4453</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2549,7 +2599,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 38.79</t>
+          <t>B- 36.91</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2733,7 +2783,9 @@
       <c r="E12" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
@@ -2773,7 +2825,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 40.30</t>
+          <t>B- 38.69</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2788,7 +2840,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2796,8 +2848,12 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -2943,7 +2999,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2965,8 +3021,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>47.72</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -2984,7 +3044,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8123</t>
+          <t>1.7929</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3098,7 +3158,7 @@
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3166,7 +3226,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26产融K3</t>
+          <t>26株洲城建PPN002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3174,60 +3234,56 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>520507.SZ</t>
-        </is>
-      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26产融K2</t>
+          <t>26株洲城建PPN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.53Y+2.00Y</t>
+          <t>4.70Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.8126</t>
+          <t>1.9017</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.8800/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司</t>
+          <t>株洲市城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B 50.87</t>
+          <t>B- 35.22</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3237,12 +3293,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3250,43 +3306,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
+          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3296,12 +3356,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3317,54 +3377,54 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3372,7 +3432,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3385,12 +3445,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3398,60 +3460,56 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>284176.SH</t>
-        </is>
-      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.9536</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 17.44</t>
+          <t>B- 38.69</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3461,12 +3519,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3474,43 +3532,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3520,12 +3582,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3535,48 +3597,60 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-      <c r="AS15" s="3"/>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3597,12 +3671,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN002</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3613,53 +3689,53 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN001</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.70Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.9017</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 36.85</t>
+          <t>B- 39.41</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3669,7 +3745,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3691,7 +3767,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3702,17 +3778,17 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3733,7 +3809,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3743,7 +3819,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3769,22 +3845,22 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
@@ -3794,7 +3870,7 @@
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3804,7 +3880,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3817,71 +3893,77 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26产融K3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
-        </is>
-      </c>
-      <c r="C17" s="3"/>
+          <t>10-08 19:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>520507.SZ</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>43.72</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>26产融K2</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>2.53Y+2.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.8191</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>宜昌产城融合投资发展有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 40.30</t>
+          <t>B 50.87</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3891,7 +3973,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3908,12 +3990,12 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -3924,23 +4006,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -3950,12 +4032,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3965,13 +4047,13 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -3986,12 +4068,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4011,12 +4093,12 @@
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4026,7 +4108,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4039,75 +4121,77 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26武临01</t>
+          <t>26中泰06</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>284214.SH</t>
+          <t>246160.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6</v>
+        <v>30.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>31.72</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24武临02</t>
+          <t>26中泰03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7737</t>
+          <t>1.6964</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B 50.28</t>
+          <t>A- 62.35</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4117,7 +4201,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4127,46 +4211,50 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z18" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4181,20 +4269,24 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4207,37 +4299,37 @@
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4270,7 +4362,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26哈城投MTN002B</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4278,56 +4370,62 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102683863.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.0310</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 40.39</t>
+          <t>C- 12.12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4337,7 +4435,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4354,12 +4452,12 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4370,23 +4468,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4401,17 +4499,17 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4422,7 +4520,7 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
@@ -4437,7 +4535,7 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4447,12 +4545,12 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4462,7 +4560,7 @@
       </c>
       <c r="AU19" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV19" s="3" t="inlineStr">
@@ -4472,7 +4570,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4485,12 +4583,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002B</t>
+          <t>26哈城投MTN002A</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4500,12 +4600,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683863.IB</t>
+          <t>102683862.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -4516,14 +4616,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -4543,7 +4643,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4553,7 +4653,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 11.52</t>
+          <t>C- 12.12</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4585,7 +4685,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4627,7 +4727,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4637,7 +4737,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4718,70 +4818,72 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002A</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683862.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.70 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>55.72</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 11.52</t>
+          <t>B- 39.74</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4791,7 +4893,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4801,46 +4903,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4850,12 +4952,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4865,53 +4967,57 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4939,14 +5045,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26中泰06</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4956,58 +5060,60 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246160.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26中泰03</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7017</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>A- 62.51</t>
+          <t>B- 38.53</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5017,7 +5123,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5027,19 +5133,23 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5047,30 +5157,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5080,12 +5186,12 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5095,64 +5201,60 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5173,12 +5275,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26常高新MTN002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5188,58 +5292,60 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>102683869.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>25常高新MTN003</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>1.51Y+N</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.9902</t>
+          <t>1.6487</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.9500</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>常高新集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 39.74</t>
+          <t>C+ 30.79</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5249,21 +5355,25 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -5271,7 +5381,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5279,26 +5389,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z23" s="3"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5308,12 +5422,12 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>常高新集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5323,64 +5437,60 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-09</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO23" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5388,12 +5498,12 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY23" s="3" t="inlineStr">
@@ -5401,12 +5511,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26宁国建投MTN002</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5416,58 +5528,60 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>102683868.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.8173</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.4900/1.4400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 38.24</t>
+          <t>C- 11.64</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5482,7 +5596,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5490,43 +5604,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5541,7 +5659,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5551,7 +5669,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5572,32 +5690,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5626,13 +5744,13 @@
         </is>
       </c>
       <c r="AZ24" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26常高新MTN002</t>
+          <t>26江苏资产SCP006</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5642,58 +5760,60 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683869.IB</t>
+          <t>012682374.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>25常高新MTN003</t>
+          <t>24江苏资产MTN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>1.51Y+N</t>
+          <t>94D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6487</t>
+          <t>1.4546</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6100</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.06</t>
+          <t>C 26.90</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5703,12 +5823,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5716,16 +5836,20 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5733,30 +5857,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
+          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5771,7 +5891,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司2026年度第二期中期票据</t>
+          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5781,10 +5901,14 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -5802,32 +5926,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5842,12 +5966,12 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY25" s="3" t="inlineStr">
@@ -5856,13 +5980,13 @@
         </is>
       </c>
       <c r="AZ25" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN002</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5870,60 +5994,56 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>102683868.IB</t>
-        </is>
-      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.8173</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 17.80</t>
+          <t>C- 23.85</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5938,7 +6058,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -5946,43 +6066,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -5997,17 +6121,17 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6028,12 +6152,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6043,17 +6167,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6086,68 +6210,72 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26江苏资产SCP006</t>
+          <t>26武临01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>012682374.IB</t>
+          <t>284214.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.0</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>48.49</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24江苏资产MTN001</t>
+          <t>24武临02</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>94D</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.4546</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.36</t>
+          <t>B 50.28</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6157,7 +6285,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6174,39 +6302,39 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
+          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6216,32 +6344,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-09</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6256,32 +6380,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6309,9 +6433,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -6321,7 +6443,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -6343,8 +6465,12 @@
           <t>1.20 ~ 2.20</t>
         </is>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="H28" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>39.49</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -6362,7 +6488,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6901</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6540,64 +6666,72 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26长寿05</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
+          <t>10-08 19:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>284131.SH</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>5.1</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>71.72</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26长寿04</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>2.2068</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>重庆长寿投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 23.85</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6607,7 +6741,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6617,19 +6751,19 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6640,23 +6774,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6666,12 +6800,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6681,13 +6815,17 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6697,7 +6835,7 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
@@ -6707,27 +6845,27 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6760,17 +6898,17 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26长寿05</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284131.SH</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -6779,34 +6917,38 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.70 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>57.72</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26长寿04</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.2277</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6816,12 +6958,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 17.85</t>
+          <t>C- 18.47</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6831,7 +6973,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6841,40 +6983,40 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6895,7 +7037,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6905,14 +7047,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6925,34 +7063,22 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3"/>
       <c r="AT30" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26广东农垦MTN002</t>
+          <t>26广东农垦MTN002(取消发行)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683870.IB</t>
+          <t>DY102683870.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -713,16 +713,18 @@
       <c r="E3" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>6.0</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>16.18</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -778,12 +780,8 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>1.23</v>
-      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -833,7 +831,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>广东省农垦集团公司2026年度第二期中期票据</t>
+          <t>广东省农垦集团公司2026年度第二期中期票据(取消发行)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -924,7 +922,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP014</t>
+          <t>26临空港投MTN006</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -934,60 +932,64 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>012682372.IB</t>
+          <t>102683864.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.38Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>15.01</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP013</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>138D</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.4846</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 27.99</t>
+          <t>B- 37.83</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -997,12 +999,12 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1011,46 +1013,46 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1065,7 +1067,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
+          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1075,7 +1077,7 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1096,37 +1098,37 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>环保工程及服务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1136,7 +1138,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
@@ -1154,7 +1156,7 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN005</t>
+          <t>26常熟投控MTN006</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1164,60 +1166,64 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683872.IB</t>
+          <t>102683866.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>24.72</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 37.83</t>
+          <t>C- 14.84</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1227,12 +1233,12 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1241,10 +1247,10 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>5.08</v>
+        <v>4.1389</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1259,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1264,17 +1270,17 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1295,7 +1301,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
+          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1305,7 +1311,7 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
@@ -1331,32 +1337,32 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV5" s="3" t="inlineStr">
@@ -1384,70 +1390,72 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN002</t>
+          <t>26吕四02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683867.IB</t>
+          <t>284163.SH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>9.5</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>47.72</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN001</t>
+          <t>26吕四01</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.44Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.5957</t>
+          <t>1.7929</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司</t>
+          <t>江苏吕四港集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 10.73</t>
+          <t>D- 1.18</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1457,33 +1465,29 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>2.06</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1499,18 +1503,18 @@
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
+          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1520,38 +1524,42 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
+          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr">
@@ -1609,14 +1617,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ6" s="3"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26广州公交SCP002</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1624,47 +1630,41 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>012682376.IB</t>
-        </is>
-      </c>
+      <c r="C7" s="3"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>24广州公交MTN001</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>1.14Y+N</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6034</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 36.53</t>
+          <t>B- 39.41</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1702,47 +1702,43 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1757,17 +1753,17 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
@@ -1788,37 +1784,37 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV7" s="3" t="inlineStr">
@@ -1828,7 +1824,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1846,70 +1842,72 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN006</t>
+          <t>26产融K3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683864.IB</t>
+          <t>520507.SZ</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>12.0</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>43.72</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26产融K2</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>2.53Y+2.00Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.8191</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>宜昌产城融合投资发展有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 37.83</t>
+          <t>B 50.87</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1919,12 +1917,12 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1932,47 +1930,43 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U8" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>4.0</v>
-      </c>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1982,28 +1976,28 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
+          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2023,32 +2017,32 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV8" s="3" t="inlineStr">
@@ -2076,55 +2070,57 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN007</t>
+          <t>26中泰06</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683865.IB</t>
+          <t>246160.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>31.72</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26中泰03</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.6964</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2134,12 +2130,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 14.84</t>
+          <t>A- 62.35</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2149,60 +2145,62 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>2.39</v>
+      </c>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z9" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2212,12 +2210,12 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2227,13 +2225,17 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
-        </is>
-      </c>
-      <c r="AK9" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM9" s="3" t="inlineStr">
@@ -2243,42 +2245,42 @@
       </c>
       <c r="AN9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
@@ -2288,7 +2290,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2306,7 +2308,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN006</t>
+          <t>26临空港投MTN005</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2316,45 +2318,49 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683866.IB</t>
+          <t>102683872.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>15.01</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2364,12 +2370,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 14.84</t>
+          <t>B- 37.83</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2379,12 +2385,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2393,10 +2399,10 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.14</v>
+        <v>5.08</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2411,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2416,17 +2422,17 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2447,7 +2453,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
+          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2457,7 +2463,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2483,32 +2489,32 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2565,8 +2571,12 @@
           <t>1.40 ~ 1.60</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>30.42</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -2791,8 +2801,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>30.72</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -2815,7 +2829,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2994,17 +3008,17 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26吕四02</t>
+          <t>26株洲城建PPN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>284163.SH</t>
+          <t>032680551.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -3013,38 +3027,40 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47.72</v>
+        <v>48.72</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26吕四01</t>
+          <t>26株洲城建PPN001</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>4.70Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7929</t>
+          <t>1.9017</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3054,12 +3070,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司</t>
+          <t>株洲市城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D- 1.18</t>
+          <t>B- 35.22</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3069,29 +3085,33 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3102,23 +3122,23 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
+          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3128,12 +3148,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3143,90 +3163,88 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY13" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO13" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ13" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN002</t>
+          <t>26广州公交SCP002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3234,56 +3252,66 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>012682376.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.30 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>19.42</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN001</t>
+          <t>24广州公交MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.70Y</t>
+          <t>1.14Y+N</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.9017</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司</t>
+          <t>广州市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 35.22</t>
+          <t>B- 36.53</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3298,7 +3326,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3307,46 +3335,46 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.03</v>
+        <v>4.66</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.0</v>
+        <v>1.7</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
+          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
+          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3361,17 +3389,17 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3392,32 +3420,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3445,14 +3473,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26江苏资产SCP006</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3460,56 +3486,66 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>012682374.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+          <t>1.20 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>33.12</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>24江苏资产MTN001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>94D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.4546</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 38.69</t>
+          <t>C 26.90</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3524,7 +3560,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3533,19 +3569,19 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.3</v>
+        <v>2.35</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.0</v>
+        <v>1.1</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3556,23 +3592,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3587,20 +3623,24 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -3618,32 +3658,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3672,13 +3712,13 @@
         </is>
       </c>
       <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3686,41 +3726,51 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>032690029.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>37.49</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.0161</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3730,12 +3780,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 39.41</t>
+          <t>C- 23.85</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3745,12 +3795,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3758,16 +3808,20 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3778,17 +3832,17 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3809,7 +3863,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3819,7 +3873,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3845,7 +3899,7 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3855,22 +3909,22 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3880,7 +3934,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3898,104 +3952,110 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26产融K3</t>
+          <t>26国联SCP014</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>520507.SZ</t>
+          <t>012682372.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.38Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>43.72</v>
+        <v>26.8</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>26国联SCP013</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>138D</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1.4846</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>无锡市国联发展(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>C 27.99</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>10-08 09:00</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>26产融K2</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>2.53Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>1.8191</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>1.8800/--</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>宜昌产城融合投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>B 50.87</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>10-08 16:00</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4006,23 +4066,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
+          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4032,75 +4092,75 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>环保工程及服务</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4108,7 +4168,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4126,57 +4186,59 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26中泰06</t>
+          <t>26海安开投MTN002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>246160.SH</t>
+          <t>102683867.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>9.5</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>31.72</v>
+        <v>37.95</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26中泰03</t>
+          <t>26海安开投MTN001</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>1.44Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6964</t>
+          <t>1.5957</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4186,12 +4248,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>海安开发区建设投资有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>A- 62.35</t>
+          <t>C- 10.73</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4201,60 +4263,60 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>2.06</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
+          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4264,12 +4326,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4279,64 +4341,60 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-10-09</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4357,12 +4415,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002B</t>
+          <t>26宁国建投MTN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4372,60 +4432,64 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683863.IB</t>
+          <t>102683868.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>52.95</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.8173</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 12.12</t>
+          <t>C- 11.64</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4440,7 +4504,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4448,37 +4512,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4499,7 +4567,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4509,7 +4577,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4520,7 +4588,7 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
@@ -4530,12 +4598,12 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4545,12 +4613,12 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4584,13 +4652,13 @@
         </is>
       </c>
       <c r="AZ19" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002A</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4600,60 +4668,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683862.IB</t>
+          <t>032680549.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>39.03</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 12.12</t>
+          <t>B- 38.69</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4663,12 +4735,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4676,43 +4748,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4727,17 +4803,17 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4748,7 +4824,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4758,32 +4834,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4812,23 +4888,23 @@
         </is>
       </c>
       <c r="AZ20" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26哈城投MTN002B</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>102683863.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4837,53 +4913,55 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>55.72</v>
+        <v>72.72</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.9933</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 39.74</t>
+          <t>C- 12.12</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4893,7 +4971,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4903,46 +4981,50 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4952,12 +5034,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4967,90 +5049,88 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY21" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO21" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ21" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26哈城投MTN002A</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5060,60 +5140,60 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>102683862.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 38.53</t>
+          <t>C- 12.12</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5136,47 +5216,43 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U22" s="4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>1.11</v>
-      </c>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5191,7 +5267,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5201,7 +5277,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5212,7 +5288,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5222,32 +5298,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5276,76 +5352,78 @@
         </is>
       </c>
       <c r="AZ22" s="4" t="n">
-        <v>0.0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26常高新MTN002</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683869.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.70 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>55.72</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25常高新MTN003</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.51Y+N</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6487</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.79</t>
+          <t>B- 39.74</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5355,25 +5433,21 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -5381,7 +5455,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5389,30 +5463,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5422,12 +5492,12 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司2026年度第二期中期票据</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5437,53 +5507,57 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5498,12 +5572,12 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY23" s="3" t="inlineStr">
@@ -5511,14 +5585,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ23" s="3"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN002</t>
+          <t>26常高新MTN002</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5528,12 +5600,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683868.IB</t>
+          <t>102683869.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -5544,44 +5616,48 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>45.49</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>25常高新MTN003</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>1.51Y+N</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.8173</t>
+          <t>1.6487</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>常高新集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 11.64</t>
+          <t>C+ 30.79</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5596,7 +5672,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5605,40 +5681,44 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.61</v>
+        <v>3.32</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z24" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
+          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5659,7 +5739,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>常高新集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5669,7 +5749,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5695,7 +5775,7 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5730,12 +5810,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5750,70 +5830,72 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26江苏资产SCP006</t>
+          <t>26武临01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>012682374.IB</t>
+          <t>284214.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>48.49</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24江苏资产MTN001</t>
+          <t>24武临02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>94D</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.4546</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C 26.90</t>
+          <t>B 50.28</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5823,12 +5905,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5836,47 +5918,43 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U25" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
+          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5886,32 +5964,28 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-09</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5926,32 +6000,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5979,71 +6053,77 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26上发02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
-        </is>
-      </c>
-      <c r="C26" s="3"/>
+          <t>10-08 19:00</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>284171.SH</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>39.49</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 23.85</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6053,60 +6133,58 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.45</v>
+      </c>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6116,12 +6194,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6131,13 +6209,13 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
@@ -6147,17 +6225,17 @@
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6167,17 +6245,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6210,7 +6288,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26武临01</t>
+          <t>26长寿05</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6220,47 +6298,47 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>284214.SH</t>
+          <t>284131.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>48.49</v>
+        <v>71.72</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24武临02</t>
+          <t>26长寿04</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>2.2068</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6270,12 +6348,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
+          <t>重庆长寿投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B 50.28</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6295,19 +6373,19 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6318,17 +6396,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
+          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6349,7 +6427,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6359,10 +6437,14 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6375,32 +6457,32 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6438,7 +6520,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26上发02</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6448,62 +6530,62 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284171.SH</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>5.2</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>39.49</v>
+        <v>57.72</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>C- 18.47</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6523,40 +6605,40 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6577,7 +6659,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6587,7 +6669,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6603,7 +6685,7 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
@@ -6613,24 +6695,12 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="3"/>
       <c r="AT28" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -6666,57 +6736,59 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26长寿05</t>
+          <t>26常熟投控MTN007</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284131.SH</t>
+          <t>102683865.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>71.72</v>
+        <v>23.72</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26长寿04</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.2068</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6726,12 +6798,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C- 14.84</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6741,29 +6813,33 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6774,23 +6850,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
+          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6800,32 +6876,28 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6835,7 +6907,7 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
@@ -6865,12 +6937,12 @@
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6880,7 +6952,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6898,57 +6970,59 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284176.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>57.72</v>
+        <v>20.61</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.9326</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6958,12 +7032,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 18.47</t>
+          <t>B- 38.53</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6973,7 +7047,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6986,21 +7060,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
@@ -7011,18 +7089,18 @@
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7032,63 +7110,75 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3"/>
-      <c r="AR30" s="3"/>
-      <c r="AS30" s="3"/>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7109,7 +7199,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-09" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-12" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-09</t>
+          <t>数据来源：DM    2026-10-12</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,8 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>16.18</v>
-      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -922,74 +918,72 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN006</t>
+          <t>26吕四02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683864.IB</t>
+          <t>284163.SH</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15.01</v>
+        <v>47.72</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26吕四01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.7929</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>江苏吕四港集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 37.83</t>
+          <t>D- 1.18</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -999,33 +993,29 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>4.0</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1036,23 +1026,23 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1062,38 +1052,42 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
+          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
@@ -1128,7 +1122,7 @@
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1138,7 +1132,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
@@ -1156,17 +1150,17 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN006</t>
+          <t>26产融K3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683866.IB</t>
+          <t>520507.SZ</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1175,55 +1169,55 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.6</v>
+        <v>12.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.6</v>
+        <v>12.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>24.72</v>
+        <v>43.72</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26产融K2</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>2.53Y+2.00Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.8191</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>宜昌产城融合投资发展有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 14.84</t>
+          <t>B- 41.27</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1233,12 +1227,12 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1247,46 +1241,44 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>4.1389</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.77</v>
+      </c>
+      <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1296,17 +1288,17 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
+          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
@@ -1317,7 +1309,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1337,7 +1329,7 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
@@ -1357,7 +1349,7 @@
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1390,7 +1382,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26吕四02</t>
+          <t>26中泰06</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1400,7 +1392,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>284163.SH</t>
+          <t>246160.SH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1409,38 +1401,38 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.0</v>
+        <v>30.0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>47.72</v>
+        <v>31.72</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26吕四01</t>
+          <t>26中泰03</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7929</t>
+          <t>1.6964</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1450,12 +1442,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>D- 1.18</t>
+          <t>B+ 57.73</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1478,43 +1470,49 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>2.39</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z6" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1529,12 +1527,12 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
@@ -1554,7 +1552,7 @@
       </c>
       <c r="AM6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN6" s="3" t="inlineStr">
@@ -1564,32 +1562,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1622,7 +1620,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26甬开投SCP002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1630,41 +1628,51 @@
           <t>10-08 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>012682375.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+          <t>1.40 ~ 1.60</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>30.42</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>22甬投01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>159D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2.0161</t>
+          <t>1.4453</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1674,12 +1682,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>宁波开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 39.41</t>
+          <t>C+ 31.27</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1689,7 +1697,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1702,43 +1710,45 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>发行人本期债务融资工具发行金额5亿元,均用来偿还发行人到期债务融资工具[26甬开投SCP001]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>国家开发银行</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1753,17 +1763,17 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>宁波开发投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
@@ -1784,37 +1794,37 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV7" s="3" t="inlineStr">
@@ -1824,7 +1834,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1842,72 +1852,74 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26产融K3</t>
+          <t>26株洲城建PPN002</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>520507.SZ</t>
+          <t>032680551.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>43.72</v>
+        <v>48.72</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26产融K2</t>
+          <t>26株洲城建PPN001</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.53Y+2.00Y</t>
+          <t>4.70Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.8191</t>
+          <t>1.9017</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.8800/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司</t>
+          <t>株洲市城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B 50.87</t>
+          <t>C+ 31.26</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1917,12 +1929,12 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1930,43 +1942,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
+          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1976,12 +1992,12 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1997,54 +2013,54 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2052,7 +2068,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2065,77 +2081,81 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26中泰06</t>
+          <t>26江苏资产SCP006</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>246160.SH</t>
+          <t>012682374.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>31.72</v>
+        <v>33.12</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26中泰03</t>
+          <t>24江苏资产MTN001</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>94D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6964</t>
+          <t>1.4546</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>A- 62.35</t>
+          <t>C- 18.99</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2145,31 +2165,33 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V9" s="3"/>
+        <v>2.35</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2177,30 +2199,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
+          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2210,12 +2228,12 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2225,64 +2243,64 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="AK9" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2303,12 +2321,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN005</t>
+          <t>26国联SCP014</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2318,49 +2338,49 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683872.IB</t>
+          <t>012682372.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.38Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15.01</v>
+        <v>26.8</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26国联SCP013</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>138D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.4846</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2370,12 +2390,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>无锡市国联发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 37.83</t>
+          <t>C 26.05</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2385,12 +2405,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2399,46 +2419,46 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>5.08</v>
+        <v>3.35</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2453,7 +2473,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
+          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2463,7 +2483,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2484,37 +2504,37 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>环保工程及服务</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2524,7 +2544,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2542,7 +2562,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26甬开投SCP002</t>
+          <t>26临空港投MTN005</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2552,12 +2572,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682375.IB</t>
+          <t>102683872.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -2568,48 +2588,48 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>30.42</v>
+        <v>15.01</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>22甬投01</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.4453</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>宁波开发投资集团有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 36.91</t>
+          <t>C+ 30.09</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2619,12 +2639,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2632,43 +2652,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额5亿元,均用来偿还发行人到期债务融资工具[26甬开投SCP001]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行</t>
+          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2683,7 +2707,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>宁波开发投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2693,7 +2717,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2714,37 +2738,37 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV11" s="3" t="inlineStr">
@@ -2754,7 +2778,7 @@
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2772,7 +2796,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN004</t>
+          <t>26常熟投控MTN006</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2782,49 +2806,49 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683871.IB</t>
+          <t>102683866.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>30.72</v>
+        <v>24.72</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN003</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7481</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2834,12 +2858,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 38.69</t>
+          <t>C- 15.65</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2849,12 +2873,12 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2863,40 +2887,40 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.74</v>
+        <v>4.1389</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.33</v>
+        <v>1.0</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
+          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2917,7 +2941,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
+          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2948,12 +2972,12 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2978,7 +3002,7 @@
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -2988,7 +3012,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3001,14 +3025,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN002</t>
+          <t>26常熟投控MTN007</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3018,49 +3040,49 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>032680551.IB</t>
+          <t>102683865.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>48.72</v>
+        <v>23.72</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN001</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.70Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.9017</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3070,12 +3092,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 35.22</t>
+          <t>C- 15.65</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3099,19 +3121,19 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.03</v>
+        <v>4.65</v>
       </c>
       <c r="V13" s="4" t="n">
         <v>2.0</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3122,23 +3144,23 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
+          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3153,12 +3175,12 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
@@ -3209,12 +3231,12 @@
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3224,7 +3246,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3237,14 +3259,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ13" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ13" s="3"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26广州公交SCP002</t>
+          <t>26哈城投MTN002A(取消发行)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3254,64 +3274,58 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>012682376.IB</t>
+          <t>DY102683862.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>19.42</v>
-      </c>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>24广州公交MTN001</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1.14Y+N</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6034</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 36.53</t>
+          <t>C- 11.11</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3326,7 +3340,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3334,47 +3348,43 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U14" s="4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3389,7 +3399,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3399,7 +3409,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3410,7 +3420,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3420,32 +3430,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3473,64 +3483,66 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26江苏资产SCP006</t>
+          <t>26武临01</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682374.IB</t>
+          <t>284214.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.0</v>
+        <v>0.6</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.0</v>
+        <v>0.6</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>33.12</v>
+        <v>48.49</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24江苏资产MTN001</t>
+          <t>24武临02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>94D</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.4546</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3540,12 +3552,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 26.90</t>
+          <t>B- 48.96</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3555,12 +3567,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3569,46 +3581,44 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
+          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3618,32 +3628,28 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-10-09</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3658,32 +3664,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3711,14 +3717,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26南通城建MTN004</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3728,12 +3732,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>032690029.IB</t>
+          <t>102683871.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -3744,48 +3748,48 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>37.49</v>
+        <v>30.72</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26南通城建MTN003</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>1.7481</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 23.85</t>
+          <t>C+ 33.89</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3795,12 +3799,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3809,46 +3813,46 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.98</v>
+        <v>4.74</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.0</v>
+        <v>3.3</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3863,17 +3867,17 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
@@ -3904,22 +3908,22 @@
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3947,12 +3951,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP014</t>
+          <t>26常高新MTN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3962,64 +3968,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682372.IB</t>
+          <t>102683869.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.38Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26.8</v>
+        <v>45.49</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP013</t>
+          <t>25常高新MTN003</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>138D</t>
+          <t>1.51Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4846</t>
+          <t>1.6487</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司</t>
+          <t>常高新集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 27.99</t>
+          <t>C 26.56</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4034,7 +4040,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4043,19 +4049,19 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.25</v>
+        <v>3.32</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4063,26 +4069,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
+          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4097,7 +4107,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
+          <t>常高新集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4107,7 +4117,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4128,32 +4138,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>环保工程及服务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4168,12 +4178,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4181,12 +4191,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN002</t>
+          <t>26临空港投MTN006</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4196,64 +4208,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683867.IB</t>
+          <t>102683864.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>9.5</v>
+        <v>10.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9.5</v>
+        <v>10.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>37.95</v>
+        <v>15.01</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN001</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1.44Y</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5957</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 10.73</t>
+          <t>C+ 30.09</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4263,12 +4275,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4277,19 +4289,19 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.67</v>
+        <v>4.23</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.06</v>
+        <v>4.0</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4300,17 +4312,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4331,7 +4343,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
+          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4341,7 +4353,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4392,7 +4404,7 @@
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4402,7 +4414,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4415,14 +4427,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN002</t>
+          <t>26海安开投MTN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4432,7 +4442,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683868.IB</t>
+          <t>102683867.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4441,55 +4451,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>52.95</v>
+        <v>37.95</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>26海安开投MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>1.44Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8173</t>
+          <t>1.5957</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>海安开发区建设投资有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 11.64</t>
+          <t>C- 14.79</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4504,7 +4514,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4513,40 +4523,40 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.61</v>
+        <v>3.6737</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
+          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4567,7 +4577,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4598,12 +4608,12 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4658,7 +4668,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26宁国建投MTN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4668,49 +4678,49 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>032680549.IB</t>
+          <t>102683868.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>39.03</v>
+        <v>52.95</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.8173</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4720,12 +4730,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 38.69</t>
+          <t>C- 13.57</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4735,12 +4745,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4749,46 +4759,46 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4803,17 +4813,17 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4839,27 +4849,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4894,7 +4904,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002B</t>
+          <t>26哈城投MTN002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4916,7 +4926,7 @@
         <v>1.5</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.5</v>
+        <v>3.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -4961,7 +4971,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 12.12</t>
+          <t>C- 11.11</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4988,7 +4998,7 @@
         <v>3.3</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>6.0</v>
+        <v>5.5</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
@@ -5039,7 +5049,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5130,70 +5140,72 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002A</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683862.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.70 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>55.72</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 12.12</t>
+          <t>B- 37.28</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5203,7 +5215,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5213,46 +5225,46 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5262,12 +5274,12 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5277,53 +5289,57 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5351,14 +5367,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26上发02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5368,62 +5382,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>284171.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>55.72</v>
+        <v>39.49</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.9933</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 39.74</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5433,7 +5447,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5446,16 +5460,18 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>4.45</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5466,17 +5482,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5497,24 +5513,20 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5522,7 +5534,7 @@
       </c>
       <c r="AM23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN23" s="3" t="inlineStr">
@@ -5532,7 +5544,7 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
@@ -5542,22 +5554,22 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5590,74 +5602,72 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26常高新MTN002</t>
+          <t>26长寿05</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683869.IB</t>
+          <t>284131.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>45.49</v>
+        <v>71.72</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25常高新MTN003</t>
+          <t>26长寿04</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.51Y+N</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6487</t>
+          <t>2.2068</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司</t>
+          <t>重庆长寿投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.79</t>
+          <t>C- 17.51</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5667,64 +5677,56 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
+          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5734,28 +5736,32 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司2026年度第二期中期票据</t>
+          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5765,12 +5771,12 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
@@ -5780,17 +5786,17 @@
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
@@ -5810,12 +5816,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5823,14 +5829,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26武临01</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5840,47 +5844,49 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>284214.SH</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>5.2</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.70 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>48.49</v>
+        <v>57.72</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24武临02</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5890,12 +5896,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B 50.28</t>
+          <t>C- 17.31</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5905,7 +5911,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5918,37 +5924,39 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>3.65</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5969,7 +5977,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5979,7 +5987,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -6005,24 +6013,12 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
       <c r="AT25" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -6058,72 +6054,74 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26上发02</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284171.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>39.49</v>
+        <v>20.61</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>C+ 32.22</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6133,7 +6131,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6143,21 +6141,23 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V26" s="3"/>
+        <v>1.86</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6168,23 +6168,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6194,75 +6194,75 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6283,62 +6283,66 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26长寿05</t>
+          <t>26广州公交SCP002</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>284131.SH</t>
+          <t>012682376.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>71.72</v>
+        <v>19.42</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26长寿04</t>
+          <t>24广州公交MTN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>1.14Y+N</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.2068</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6348,12 +6352,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司</t>
+          <t>广州市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C+ 32.75</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6363,56 +6367,60 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
+          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6422,32 +6430,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-06</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6457,37 +6461,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6520,72 +6524,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284176.SH</t>
+          <t>032690029.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>57.72</v>
+        <v>37.49</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9326</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 18.47</t>
+          <t>C 25.22</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6595,12 +6601,12 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -6608,43 +6614,47 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+      <c r="U28" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6654,12 +6664,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6669,13 +6679,13 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6690,20 +6700,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3"/>
-      <c r="AR28" s="3"/>
-      <c r="AS28" s="3"/>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6736,7 +6758,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN007</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6746,49 +6768,49 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683865.IB</t>
+          <t>032690030.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>23.72</v>
+        <v>27.01</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6798,12 +6820,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 14.84</t>
+          <t>B- 39.76</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6813,12 +6835,12 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6827,19 +6849,17 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.94</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6850,23 +6870,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6881,17 +6901,17 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6917,32 +6937,32 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6970,7 +6990,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6980,64 +7000,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>032680549.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>20.61</v>
+        <v>39.03</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 38.53</t>
+          <t>C+ 33.89</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7047,12 +7067,12 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7061,19 +7081,19 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.11</v>
+        <v>1.0</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7084,23 +7104,23 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7115,17 +7135,17 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7146,32 +7166,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7200,7 +7220,7 @@
         </is>
       </c>
       <c r="AZ30" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -4904,17 +4904,17 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683863.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4923,55 +4923,53 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.70 ~ 2.60</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>72.72</v>
+        <v>55.72</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 11.11</t>
+          <t>B- 37.28</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4981,7 +4979,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4991,50 +4989,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>5.5</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5044,12 +5038,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5059,53 +5053,57 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5133,14 +5131,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26上发02</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5150,62 +5146,62 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>284171.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>55.72</v>
+        <v>39.49</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.9933</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 37.28</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5215,7 +5211,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5228,16 +5224,18 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>4.45</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5248,17 +5246,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5279,24 +5277,20 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5304,7 +5298,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5314,7 +5308,7 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5324,22 +5318,22 @@
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5372,7 +5366,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26上发02</t>
+          <t>26长寿05</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5382,62 +5376,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>284171.SH</t>
+          <t>284131.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10.0</v>
+        <v>5.1</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>39.49</v>
+        <v>71.72</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>26长寿04</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>2.2068</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>重庆长寿投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>C- 17.51</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5447,7 +5441,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5460,39 +5454,37 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>4.45</v>
-      </c>
+      <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
+          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5513,7 +5505,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5523,10 +5515,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5544,27 +5540,27 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
@@ -5602,7 +5598,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26长寿05</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5612,7 +5608,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>284131.SH</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5621,38 +5617,40 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>5.2</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.70 ~ 2.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>71.72</v>
+        <v>57.72</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26长寿04</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.2068</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5662,12 +5660,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 17.51</t>
+          <t>C- 17.31</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5677,7 +5675,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5687,40 +5685,42 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U24" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>3.65</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5751,14 +5751,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5771,34 +5767,22 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ24" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3"/>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="3"/>
       <c r="AT24" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -5834,74 +5818,74 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>284176.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>57.72</v>
+        <v>20.61</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9326</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 17.31</t>
+          <t>C+ 32.22</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5911,7 +5895,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5925,22 +5909,24 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V25" s="3"/>
+        <v>1.86</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
@@ -5951,18 +5937,18 @@
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5972,63 +5958,75 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3"/>
-      <c r="AS25" s="3"/>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6049,12 +6047,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ25" s="3"/>
+      <c r="AZ25" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26广州公交SCP002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6064,64 +6064,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>012682376.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20.61</v>
+        <v>19.42</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>24广州公交MTN001</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>1.14Y+N</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>广州市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.22</t>
+          <t>C+ 32.75</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6145,19 +6145,19 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.86</v>
+        <v>4.66</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6168,17 +6168,17 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6230,32 +6230,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6283,14 +6283,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ26" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ26" s="3"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26广州公交SCP002</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6300,64 +6298,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>012682376.IB</t>
+          <t>032690029.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>19.42</v>
+        <v>37.49</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24广州公交MTN001</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.14Y+N</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6034</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.75</t>
+          <t>C 25.22</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6372,7 +6370,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -6381,46 +6379,46 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.66</v>
+        <v>4.98</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.05</v>
+        <v>1.0</v>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6435,17 +6433,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6466,32 +6464,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6524,7 +6522,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6534,12 +6532,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>032690029.IB</t>
+          <t>032690030.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -6550,48 +6548,48 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>37.49</v>
+        <v>27.01</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 25.22</t>
+          <t>B- 39.76</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6601,12 +6599,12 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -6615,19 +6613,17 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.94</v>
+      </c>
+      <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6638,17 +6634,17 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6669,7 +6665,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6679,7 +6675,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6705,7 +6701,7 @@
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6715,22 +6711,22 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6740,7 +6736,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6758,7 +6754,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6768,64 +6764,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>032690030.IB</t>
+          <t>032680549.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>27.01</v>
+        <v>39.03</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.0161</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 39.76</t>
+          <t>C+ 33.89</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6835,12 +6831,12 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6849,38 +6845,40 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>4.3</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6901,7 +6899,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6911,7 +6909,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6932,37 +6930,37 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6972,7 +6970,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6985,12 +6983,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ29" s="3"/>
+      <c r="AZ29" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26哈城投MTN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7000,64 +7000,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>032680549.IB</t>
+          <t>102683863.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>39.03</v>
+        <v>72.72</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.89</t>
+          <t>C- 11.11</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7081,46 +7081,46 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.0</v>
+        <v>5.5</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="AZ30" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-12" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-12</t>
+          <t>数据来源：DM    2026-10-13</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 19.30</t>
+          <t>C- 16.30</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26吕四02</t>
+          <t>26产融K3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -928,62 +928,64 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>284163.SH</t>
+          <t>520507.SZ</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>12.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>12.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>47.72</v>
+        <v>43.72</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26吕四01</t>
+          <t>26产融K2</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>2.53Y+2.00Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.7929</t>
+          <t>1.8191</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司</t>
+          <t>宜昌产城融合投资发展有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>D- 1.18</t>
+          <t>C+ 33.41</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -993,7 +995,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1003,40 +1005,42 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>2.77</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1052,12 +1056,12 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1067,14 +1071,10 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
@@ -1097,32 +1097,32 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>金属非金属新材料</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
@@ -1150,108 +1150,108 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26产融K3</t>
+          <t>26甬开投SCP002</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>520507.SZ</t>
+          <t>012682375.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 1.60</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>43.72</v>
+        <v>30.42</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>22甬投01</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>159D</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1.4453</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>宁波开发投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.22</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>10-08 09:00</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>26产融K2</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2.53Y+2.00Y</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>1.8191</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>1.8800/--</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>宜昌产城融合投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>B- 41.27</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>10-08 16:00</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>2.77</v>
+        <v>4.0</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1262,23 +1262,23 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将8.40亿元用于置换前期基金出资,3.60亿元用于偿还有息债务。</t>
+          <t>发行人本期债务融资工具发行金额5亿元,均用来偿还发行人到期债务融资工具[26甬开投SCP001]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>国家开发银行</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1288,75 +1288,75 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>宜昌产城融合投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>宁波开发投资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>金属非金属新材料</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX5" s="3" t="inlineStr">
@@ -1382,17 +1382,17 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26中泰06</t>
+          <t>26株洲城建PPN002</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>246160.SH</t>
+          <t>032680551.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1401,53 +1401,55 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>31.72</v>
+        <v>48.72</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26中泰03</t>
+          <t>26株洲城建PPN001</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>4.70Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.6964</t>
+          <t>1.9017</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>株洲市城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.73</t>
+          <t>C 29.57</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1457,62 +1459,60 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V6" s="3"/>
+        <v>3.03</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
+          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1522,79 +1522,75 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ6" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1615,12 +1611,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26甬开投SCP002</t>
+          <t>26江苏资产SCP006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1630,64 +1628,64 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>012682375.IB</t>
+          <t>012682374.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.60</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>30.42</v>
+        <v>33.12</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>22甬投01</t>
+          <t>24江苏资产MTN001</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>159D</t>
+          <t>94D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.4453</t>
+          <t>1.4546</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>宁波开发投资集团有限公司</t>
+          <t>江苏资产管理有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.27</t>
+          <t>C- 18.99</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1697,12 +1695,12 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1711,17 +1709,19 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="V7" s="3"/>
+        <v>2.35</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1732,17 +1732,17 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额5亿元,均用来偿还发行人到期债务融资工具[26甬开投SCP001]</t>
+          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行</t>
+          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>宁波开发投资集团有限公司2026年度第二期超短期融资券</t>
+          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1773,10 +1773,14 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
-        </is>
-      </c>
-      <c r="AK7" s="3"/>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -1794,32 +1798,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1847,12 +1851,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN002</t>
+          <t>26国联SCP014</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1862,64 +1868,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>032680551.IB</t>
+          <t>012682372.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.38Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>48.72</v>
+        <v>26.8</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN001</t>
+          <t>26国联SCP013</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.70Y</t>
+          <t>138D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.9017</t>
+          <t>1.4846</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司</t>
+          <t>无锡市国联发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.26</t>
+          <t>C 25.97</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1934,7 +1940,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1943,46 +1949,46 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>2.1</v>
+        <v>1.0</v>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模为0亿元,发行金额上限为10亿元,拟用于偿还发行人存量债务融资工具[23株洲城建MTN004]</t>
+          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司,浙商银行股份有限公司,北京银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1997,17 +2003,17 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -2028,12 +2034,12 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -2043,17 +2049,17 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>环保工程及服务</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2081,14 +2087,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26江苏资产SCP006</t>
+          <t>26临空港投MTN005</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2098,64 +2102,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>012682374.IB</t>
+          <t>102683872.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>33.12</v>
+        <v>15.01</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>24江苏资产MTN001</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>94D</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.4546</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C+ 31.67</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2165,12 +2169,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2179,10 +2183,10 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.35</v>
+        <v>5.08</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.1</v>
+        <v>10.0</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2191,34 +2195,34 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元,募集资金拟用于偿还发行人债务融资工具本金。[25江苏资产MTN005]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2233,7 +2237,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>江苏资产管理有限公司2026年度第六期超短期融资券</t>
+          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2243,14 +2247,10 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-10-09</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
           <t>2026-10-10</t>
@@ -2268,37 +2268,37 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2321,14 +2321,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP014</t>
+          <t>26常熟投控MTN006</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2338,49 +2336,49 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>012682372.IB</t>
+          <t>102683866.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.38Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.0</v>
+        <v>3.6</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.0</v>
+        <v>3.6</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26.8</v>
+        <v>24.72</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26国联SCP013</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>138D</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4846</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2390,12 +2388,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 26.05</t>
+          <t>C- 15.34</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2410,7 +2408,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2419,46 +2417,46 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.35</v>
+        <v>4.1389</v>
       </c>
       <c r="V10" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金2.00亿元,所募集资金拟用于偿还发行人子公司有息债务</t>
+          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2473,7 +2471,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>无锡市国联发展(集团)有限公司2026年度第十四期超短期融资券</t>
+          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2483,7 +2481,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2504,12 +2502,12 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
@@ -2519,22 +2517,22 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>环保工程及服务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2544,7 +2542,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2562,7 +2560,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN005</t>
+          <t>26常熟投控MTN007</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2572,64 +2570,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683872.IB</t>
+          <t>102683865.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15.01</v>
+        <v>23.72</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.09</t>
+          <t>C- 15.34</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2639,12 +2637,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2653,10 +2651,10 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.08</v>
+        <v>4.65</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
@@ -2665,7 +2663,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2676,17 +2674,17 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2707,7 +2705,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
+          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2717,7 +2715,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2743,32 +2741,32 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV11" s="3" t="inlineStr">
@@ -2796,7 +2794,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN006</t>
+          <t>26哈城投MTN002A(取消发行)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2806,64 +2804,58 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683866.IB</t>
+          <t>DY102683862.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>3.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>24.72</v>
-      </c>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 15.65</t>
+          <t>C- 15.69</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2878,7 +2870,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2886,20 +2878,16 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U12" s="4" t="n">
-        <v>4.1389</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2910,17 +2898,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2941,7 +2929,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2951,7 +2939,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2962,7 +2950,7 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2982,27 +2970,27 @@
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -3012,7 +3000,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3025,64 +3013,66 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN007</t>
+          <t>26武临01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683865.IB</t>
+          <t>284214.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.0</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.0</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>23.72</v>
+        <v>48.49</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>24武临02</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3092,12 +3082,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 15.65</t>
+          <t>B- 48.96</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3107,12 +3097,12 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3121,19 +3111,17 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3144,23 +3132,23 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3170,28 +3158,28 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3206,37 +3194,37 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3246,7 +3234,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3264,7 +3252,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002A(取消发行)</t>
+          <t>26南通城建MTN004</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3274,58 +3262,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DY102683862.IB</t>
+          <t>102683871.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>30.72</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26南通城建MTN003</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.7481</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 11.11</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3335,12 +3329,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3348,37 +3342,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3399,7 +3397,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
+          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3409,7 +3407,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3420,7 +3418,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3430,32 +3428,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3484,80 +3482,80 @@
         </is>
       </c>
       <c r="AZ14" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26武临01</t>
+          <t>26常高新MTN002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>284214.SH</t>
+          <t>102683869.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6</v>
+        <v>10.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>48.49</v>
+        <v>45.49</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>24武临02</t>
+          <t>25常高新MTN003</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>1.51Y+N</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>1.6487</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
+          <t>常高新集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 48.96</t>
+          <t>C- 23.39</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3567,12 +3565,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3581,44 +3579,50 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>3.32</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z15" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
+          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3628,17 +3632,17 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>常高新集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
@@ -3649,54 +3653,54 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3704,12 +3708,12 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY15" s="3" t="inlineStr">
@@ -3717,12 +3721,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN004</t>
+          <t>26临空港投MTN006</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3732,64 +3738,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683871.IB</t>
+          <t>102683864.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>30.72</v>
+        <v>15.01</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN003</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7481</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7200</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.89</t>
+          <t>C+ 31.67</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3799,12 +3805,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3813,40 +3819,40 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.74</v>
+        <v>4.23</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.3</v>
+        <v>4.0</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3867,7 +3873,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
+          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3877,7 +3883,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3898,37 +3904,37 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3938,7 +3944,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3951,14 +3957,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26常高新MTN002</t>
+          <t>26海安开投MTN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3968,64 +3972,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683869.IB</t>
+          <t>102683867.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>45.49</v>
+        <v>37.95</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25常高新MTN003</t>
+          <t>26海安开投MTN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.51Y+N</t>
+          <t>1.44Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6487</t>
+          <t>1.5957</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司</t>
+          <t>海安开发区建设投资有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 26.56</t>
+          <t>C- 20.15</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4040,7 +4044,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4049,44 +4053,40 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.32</v>
+        <v>3.6737</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
+          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司2026年度第二期中期票据</t>
+          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN006</t>
+          <t>26宁国建投MTN002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683864.IB</t>
+          <t>102683868.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -4224,48 +4224,48 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15.01</v>
+        <v>52.95</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.8173</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.09</t>
+          <t>C- 19.65</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4289,40 +4289,40 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>4.23</v>
+        <v>2.61</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>4.0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
+          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4427,79 +4427,81 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN002</t>
+          <t>26长寿05</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683867.IB</t>
+          <t>284131.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.5</v>
+        <v>5.1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9.5</v>
+        <v>5.1</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>37.95</v>
+        <v>71.72</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN001</t>
+          <t>26长寿04</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.44Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5957</t>
+          <t>2.2068</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司</t>
+          <t>重庆长寿投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 14.79</t>
+          <t>C- 17.94</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4509,25 +4511,23 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.6737</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.63</v>
-      </c>
+        <v>2.08</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>2.07%~2.17%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4546,23 +4546,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
+          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4572,28 +4572,32 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
+          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4603,7 +4607,7 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -4613,22 +4617,22 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
@@ -4661,66 +4665,64 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN002</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683868.IB</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.0</v>
+        <v>5.2</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.70 ~ 2.80</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>52.95</v>
+        <v>57.72</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN001</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8173</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4730,12 +4732,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 13.57</t>
+          <t>C- 18.28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4745,12 +4747,12 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4759,19 +4761,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4782,23 +4782,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4808,28 +4808,28 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4849,24 +4849,12 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3"/>
       <c r="AT20" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -4897,79 +4885,79 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.97</v>
+        <v>1.36</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>55.72</v>
+        <v>20.61</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.9933</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 37.28</t>
+          <t>C+ 30.88</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4979,7 +4967,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4989,19 +4977,23 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5012,23 +5004,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5038,12 +5030,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5053,155 +5045,155 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY21" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AO21" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ21" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>综合建筑施工</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26上发02</t>
+          <t>26广州公交SCP002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>284171.SH</t>
+          <t>012682376.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>39.49</v>
+        <v>19.42</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>24广州公交MTN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>1.14Y+N</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>广州市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>B- 37.67</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5211,31 +5203,33 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V22" s="3"/>
+        <v>4.66</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5246,23 +5240,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
+          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5272,28 +5266,28 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -5303,7 +5297,7 @@
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
@@ -5313,27 +5307,27 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5366,72 +5360,74 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26长寿05</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>284131.SH</t>
+          <t>032690029.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>71.72</v>
+        <v>37.49</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26长寿04</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.2068</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 17.51</t>
+          <t>C- 23.72</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5441,29 +5437,33 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.07%~2.17%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5474,23 +5474,23 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过5.1亿元(含5.1亿元)。本期债券募集资金扣除发行费用后,拟全部用于偿还“26长寿D2”公司债券本金[26长寿D2]</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5515,17 +5515,13 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-09</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5535,7 +5531,7 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
@@ -5545,27 +5541,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5598,59 +5594,59 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>284176.SH</t>
+          <t>032690030.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>57.72</v>
+        <v>27.01</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.9326</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5660,12 +5656,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 17.31</t>
+          <t>C+ 33.50</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5675,7 +5671,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5689,44 +5685,44 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5736,12 +5732,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5751,13 +5747,13 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5772,7 +5768,7 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
@@ -5780,9 +5776,21 @@
           <t>7</t>
         </is>
       </c>
-      <c r="AQ24" s="3"/>
-      <c r="AR24" s="3"/>
-      <c r="AS24" s="3"/>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -5790,7 +5798,7 @@
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5818,7 +5826,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5828,64 +5836,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>032680549.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20.61</v>
+        <v>39.03</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.22</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5895,12 +5903,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5909,19 +5917,19 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.11</v>
+        <v>1.0</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5932,23 +5940,23 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5963,17 +5971,17 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5994,32 +6002,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6048,13 +6056,13 @@
         </is>
       </c>
       <c r="AZ25" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26广州公交SCP002</t>
+          <t>26哈城投MTN002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6064,64 +6072,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>012682376.IB</t>
+          <t>102683863.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.42</v>
+        <v>72.72</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24广州公交MTN001</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.14Y+N</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6034</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.75</t>
+          <t>C- 15.69</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6145,46 +6153,46 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.66</v>
+        <v>3.3</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6199,7 +6207,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
+          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6209,7 +6217,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6220,7 +6228,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -6230,32 +6238,32 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6283,79 +6291,81 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>032690029.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>37.49</v>
+        <v>55.72</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 25.22</t>
+          <t>C+ 33.96</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6365,60 +6375,58 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.06</v>
+      </c>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6428,68 +6436,72 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6522,74 +6534,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26上发02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>032690030.IB</t>
+          <t>284171.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>27.01</v>
+        <v>39.49</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.0161</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 39.76</t>
+          <t>C+ 34.41</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6599,7 +6611,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6609,48 +6621,48 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.94</v>
+        <v>4.45</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6660,12 +6672,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6675,13 +6687,13 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2029-10-12</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6691,17 +6703,17 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6711,12 +6723,12 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6726,7 +6738,7 @@
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6736,7 +6748,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6754,74 +6766,74 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26吕四02</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>032680549.IB</t>
+          <t>284163.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>39.03</v>
+        <v>47.72</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>26吕四01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.7929</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>江苏吕四港集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.89</t>
+          <t>D- 0.94</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6831,38 +6843,36 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.83</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
@@ -6873,18 +6883,18 @@
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6894,12 +6904,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6909,53 +6919,57 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6983,24 +6997,22 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ29" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ29" s="3"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002</t>
+          <t>26中泰06</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683863.IB</t>
+          <t>246160.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -7009,40 +7021,40 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.5</v>
+        <v>30.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>72.72</v>
+        <v>31.72</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26中泰03</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.6964</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7052,12 +7064,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 11.11</t>
+          <t>B 53.19</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7067,7 +7079,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7077,50 +7089,52 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>5.5</v>
-      </c>
+        <v>2.3867</v>
+      </c>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z30" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7130,12 +7144,12 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7145,53 +7159,57 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7219,9 +7237,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -4670,74 +4670,74 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26紫科02</t>
+          <t>26苏农垦SCP021</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>284176.SH</t>
+          <t>012682373.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.80</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>57.72</v>
+        <v>20.61</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26紫科01</t>
+          <t>26苏农垦SCP020</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.47Y</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.9326</t>
+          <t>1.4603</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司</t>
+          <t>江苏省农垦集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 18.28</t>
+          <t>C+ 30.88</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>10-08 15:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4761,22 +4761,24 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>1.86</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.11</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
@@ -4787,18 +4789,18 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
+          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4808,28 +4810,28 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4844,20 +4846,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
-      <c r="AS20" s="3"/>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4885,12 +4899,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP021</t>
+          <t>26广州公交SCP002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4900,64 +4916,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682373.IB</t>
+          <t>012682376.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20.61</v>
+        <v>19.42</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26苏农垦SCP020</t>
+          <t>24广州公交MTN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>1.14Y+N</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.4603</t>
+          <t>1.6034</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司</t>
+          <t>广州市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.88</t>
+          <t>B- 37.67</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4972,7 +4988,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4981,19 +4997,19 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.86</v>
+        <v>4.66</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -5004,17 +5020,17 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元，用于偿还发行人存量负债</t>
+          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5035,7 +5051,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>江苏省农垦集团有限公司2026年度第二十一期超短期融资券</t>
+          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5045,7 +5061,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-07-06</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -5066,32 +5082,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5119,14 +5135,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26广州公交SCP002</t>
+          <t>26常交通PPN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5136,64 +5150,64 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>012682376.IB</t>
+          <t>032690029.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>19.42</v>
+        <v>37.49</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24广州公交MTN001</t>
+          <t>26常交通PPN002</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>1.14Y+N</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6034</t>
+          <t>1.7136</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司</t>
+          <t>常州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 37.67</t>
+          <t>C- 23.72</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5208,7 +5222,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5217,46 +5231,46 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.66</v>
+        <v>4.98</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.05</v>
+        <v>1.0</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行10亿元超短期融资券,全部用于偿还债务融资工具。【26广州公交SCP001】</t>
+          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5271,17 +5285,17 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>广州市公共交通集团有限公司2026年度第二期超短期融资券</t>
+          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-07-06</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5302,32 +5316,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5360,7 +5374,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN003</t>
+          <t>26成都经开PPN004</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5370,12 +5384,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>032690029.IB</t>
+          <t>032690030.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -5386,48 +5400,48 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>37.49</v>
+        <v>27.01</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26常交通PPN002</t>
+          <t>26成经02</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.7136</t>
+          <t>2.0161</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司</t>
+          <t>成都经开产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 23.72</t>
+          <t>C+ 33.50</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5437,12 +5451,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 13:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5451,19 +5465,17 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.94</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5474,17 +5486,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行金额为5亿元,拟用于偿还发行人本部存量债务融资工具本金[23常交通PPN003]</t>
+          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司,宁波银行股份有限公司,江苏江南农村商业银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5505,7 +5517,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>常州市交通产业集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5515,7 +5527,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5541,7 +5553,7 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
@@ -5551,22 +5563,22 @@
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV23" s="3" t="inlineStr">
@@ -5576,7 +5588,7 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
@@ -5594,7 +5606,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26成都经开PPN004</t>
+          <t>26南通城建PPN002</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5604,64 +5616,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>032690030.IB</t>
+          <t>032680549.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>4Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27.01</v>
+        <v>39.03</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26成经02</t>
+          <t>26南通城建PPN001</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>3.86Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.0161</t>
+          <t>1.7519</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.50</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5671,12 +5683,12 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>10-08 13:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5685,38 +5697,40 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="V24" s="3"/>
+        <v>4.3</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>募集资金用于偿还回售/到期的债务融资工具本金[23蓉经开PPN002]</t>
+          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天津银行股份有限公司</t>
+          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5737,7 +5751,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>成都经开产业投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5747,7 +5761,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2030-10-09</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5768,37 +5782,37 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5808,7 +5822,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5821,12 +5835,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN002</t>
+          <t>26哈城投MTN002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5836,64 +5852,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>032680549.IB</t>
+          <t>102683863.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>4Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.0</v>
+        <v>1.5</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>39.03</v>
+        <v>72.72</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26南通城建PPN001</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>3.86Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7519</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>C- 15.69</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5903,12 +5919,12 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -5917,46 +5933,46 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.0</v>
+        <v>5.5</v>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行4.00亿元,募集资金用于偿还发行人存量债务融资工具本金。[23南通城建MTN003]</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5971,17 +5987,17 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第二期定向债务融资工具</t>
+          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5992,7 +6008,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -6002,32 +6018,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6056,23 +6072,23 @@
         </is>
       </c>
       <c r="AZ25" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002</t>
+          <t>26湘建K5</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683863.IB</t>
+          <t>246102.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6081,55 +6097,55 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.5</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.70 ~ 2.60</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>72.72</v>
+        <v>55.72</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.9933</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>1.9900/1.9800</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 15.69</t>
+          <t>C+ 33.96</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6139,7 +6155,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6149,50 +6165,48 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>5.5</v>
-      </c>
+        <v>2.06</v>
+      </c>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6202,12 +6216,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6217,53 +6231,57 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t/>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6291,14 +6309,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ26" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ26" s="3"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26湘建K5</t>
+          <t>26上发02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6308,64 +6324,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>246102.SH</t>
+          <t>284171.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>55.72</v>
+        <v>39.49</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26上发01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.9933</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>杭州上城区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.96</t>
+          <t>C+ 34.41</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6375,7 +6391,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6389,17 +6405,17 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.06</v>
+        <v>4.45</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6410,17 +6426,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6441,24 +6457,20 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-12</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6466,7 +6478,7 @@
       </c>
       <c r="AM27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN27" s="3" t="inlineStr">
@@ -6476,7 +6488,7 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
@@ -6486,22 +6498,22 @@
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6534,7 +6546,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26上发02</t>
+          <t>26吕四02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6544,64 +6556,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284171.SH</t>
+          <t>284163.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>39.49</v>
+        <v>47.72</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26上发01</t>
+          <t>26吕四01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>1.7929</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司</t>
+          <t>江苏吕四港集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.41</t>
+          <t>D- 0.94</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6625,38 +6637,38 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人存量公司债券[23上发02]</t>
+          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6677,7 +6689,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州上城区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6687,10 +6699,14 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-10-12</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2031-10-12</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6698,7 +6714,7 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6708,12 +6724,12 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6723,12 +6739,12 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6766,7 +6782,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26吕四02</t>
+          <t>26中泰06</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6776,7 +6792,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284163.SH</t>
+          <t>246160.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6785,40 +6801,40 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.0</v>
+        <v>30.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.0</v>
+        <v>30.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>47.72</v>
+        <v>31.72</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26吕四01</t>
+          <t>26中泰03</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7929</t>
+          <t>1.6964</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6828,12 +6844,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D- 0.94</t>
+          <t>B 53.19</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6857,44 +6873,48 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.83</v>
+        <v>2.3867</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z29" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券为无异议函项下的第二期发行,发行规模不超过7亿元(含),募集资金拟全部用于偿还回售公司债券本金[23吕四02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6909,12 +6929,12 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>江苏吕四港集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
@@ -6934,7 +6954,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6944,32 +6964,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7002,7 +7022,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中泰06</t>
+          <t>26紫科02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7012,7 +7032,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>246160.SH</t>
+          <t>284176.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -7021,40 +7041,40 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>30.0</v>
+        <v>5.2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>30.0</v>
+        <v>5.2</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.70 ~ 2.80</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>31.72</v>
+        <v>57.72</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26中泰03</t>
+          <t>26紫科01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>4.47Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6964</t>
+          <t>1.9326</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7064,12 +7084,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>南京紫金山科技城经济发展有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B 53.19</t>
+          <t>C- 18.28</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7089,52 +7109,48 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.3867</v>
+        <v>3.65</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过30亿元(含)用于偿还到期公司债券本金[23中泰02]</t>
+          <t>本期发行金额不超过5.20亿元(含5.20亿元)，本期公司债券募集资金拟全部用于偿还公司债券本金[23未来05]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>南京证券股份有限公司,招商证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7149,27 +7165,23 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>南京紫金山科技城经济发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-10-12</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-09</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7179,37 +7191,25 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3"/>
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3"/>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 16.30</t>
+          <t>C- 14.11</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.41</t>
+          <t>B- 39.31</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.22</t>
+          <t>C+ 33.53</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C 29.57</t>
+          <t>C 29.17</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 18.99</t>
+          <t>C- 19.12</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C 25.97</t>
+          <t>C 26.32</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.67</t>
+          <t>C+ 34.81</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 15.34</t>
+          <t>C- 12.76</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 15.34</t>
+          <t>C- 12.76</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 15.69</t>
+          <t>C- 16.36</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 48.96</t>
+          <t>A- 63.75</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>C 27.81</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 23.39</t>
+          <t>C- 23.37</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.67</t>
+          <t>C+ 34.81</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 20.15</t>
+          <t>C- 21.14</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 19.65</t>
+          <t>C 29.47</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 17.94</t>
+          <t>C- 17.72</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.88</t>
+          <t>C+ 31.76</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 37.67</t>
+          <t>C 29.23</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 23.72</t>
+          <t>C- 22.73</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.50</t>
+          <t>C+ 30.47</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>C 27.81</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 15.69</t>
+          <t>C- 16.36</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.96</t>
+          <t>C+ 31.41</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B 53.19</t>
+          <t>B 52.17</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 18.28</t>
+          <t>C- 15.43</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-08.xlsx
+++ b/data/credit_bond_all_2026-10-08.xlsx
@@ -2092,7 +2092,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN005</t>
+          <t>26常熟投控MTN006</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2102,64 +2102,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683872.IB</t>
+          <t>102683866.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.0</v>
+        <v>3.6</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15.01</v>
+        <v>24.72</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26常熟投控MTN005</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>2.88Y+2.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.6676</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>常熟市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.81</t>
+          <t>C- 12.76</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>5.08</v>
+        <v>4.1389</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2206,17 +2206,17 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
+          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2273,32 +2273,32 @@
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN006</t>
+          <t>26常熟投控MTN007</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683866.IB</t>
+          <t>102683865.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.6</v>
+        <v>2.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.6</v>
+        <v>2.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24.72</v>
+        <v>23.72</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.1389</v>
+        <v>4.65</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额3.6亿元，募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第六期中期票据</t>
+          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2560,7 +2560,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN007</t>
+          <t>26哈城投MTN002A(取消发行)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2570,64 +2570,58 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683865.IB</t>
+          <t>DY102683862.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>23.72</v>
-      </c>
+          <t>1.60 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26常熟投控MTN005</t>
+          <t>26哈城投MTN001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+2.00Y</t>
+          <t>2.71Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6676</t>
+          <t>1.7863</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7500</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司</t>
+          <t>哈尔滨市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 12.76</t>
+          <t>C- 16.36</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2642,7 +2636,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2650,20 +2644,16 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U11" s="4" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2674,17 +2664,17 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>黑龙江省-哈尔滨市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发2.00亿元,募集资金用途为全部用于偿还发行人本部到期债务融资工具本金。[23常熟发投PPN003]</t>
+          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2705,7 +2695,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>常熟市投资控股集团有限公司2026年度第七期中期票据</t>
+          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2715,7 +2705,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2726,7 +2716,7 @@
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2746,27 +2736,27 @@
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV11" s="3" t="inlineStr">
@@ -2776,7 +2766,7 @@
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2789,22 +2779,24 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN002A(取消发行)</t>
+          <t>26武临01</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>10-08 18:00</t>
+          <t>10-08 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>DY102683862.IB</t>
+          <t>284214.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2813,49 +2805,55 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>48.49</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26哈城投MTN001</t>
+          <t>24武临02</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.71Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7863</t>
+          <t>1.7587</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 16.36</t>
+          <t>A- 63.75</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2865,7 +2863,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 16:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2878,7 +2876,9 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2898,23 +2898,23 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省-哈尔滨市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行30,000.00万元,全部用于偿还发行人本部到期的债务融资工具本金[23哈城投PPN002]</t>
+          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,光大证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2924,17 +2924,17 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>哈尔滨市城市建设投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
+          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
@@ -2945,12 +2945,12 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
@@ -3013,81 +3013,79 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26武临01</t>
+          <t>26南通城建MTN004</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>10-08 19:00</t>
+          <t>10-08 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>284214.SH</t>
+          <t>102683871.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>5.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6</v>
+        <v>5.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>48.49</v>
+        <v>30.72</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>24武临02</t>
+          <t>26南通城建MTN003</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7587</t>
+          <t>1.7481</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
+          <t>南通城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>A- 63.75</t>
+          <t>C 27.81</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3097,12 +3095,12 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>10-08 16:00</t>
+          <t>10-08 10:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3111,44 +3109,46 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>4.74</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,发行人拟用于偿还存量公司债券本金[21武临01]</t>
+          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3158,28 +3158,28 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3199,27 +3199,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3247,12 +3247,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN004</t>
+          <t>26常高新MTN002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3262,19 +3264,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683871.IB</t>
+          <t>102683869.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -3282,44 +3284,44 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>30.72</v>
+        <v>45.49</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26南通城建MTN003</t>
+          <t>25常高新MTN003</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>1.51Y+N</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7481</t>
+          <t>1.6487</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7200</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司</t>
+          <t>常高新集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 27.81</t>
+          <t>C- 23.37</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3329,12 +3331,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>10-08 10:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3343,19 +3345,19 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.74</v>
+        <v>3.32</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3363,20 +3365,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z14" s="3"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期发行5.00亿元,募集资金用于偿还发行人本部存量债务融资工具本金[23南通城建MTN003]</t>
+          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3397,7 +3403,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>南通城市建设集团有限公司2026年度第四期中期票据</t>
+          <t>常高新集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3407,7 +3413,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t>2029-10-09</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3433,27 +3439,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3468,12 +3474,12 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY14" s="3" t="inlineStr">
@@ -3488,7 +3494,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26常高新MTN002</t>
+          <t>26临空港投MTN006</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3498,12 +3504,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683869.IB</t>
+          <t>102683864.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -3514,48 +3520,48 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>45.49</v>
+        <v>15.01</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25常高新MTN003</t>
+          <t>26临空港投MTN004</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>1.51Y+N</t>
+          <t>4.96Y+5.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6487</t>
+          <t>1.8338</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.8400/1.8000</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司</t>
+          <t>武汉临空港投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 23.37</t>
+          <t>C+ 34.81</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3565,12 +3571,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>10-08 09:00</t>
+          <t>10-08 14:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3579,44 +3585,40 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.32</v>
+        <v>4.23</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.5</v>
+        <v>4.0</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，募集资金用于偿还发行人本级存量债务融资工具本金[23常高新MTN002]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,江苏银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3637,7 +3639,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>常高新集团有限公司2026年度第二期中期票据</t>
+          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3647,7 +3649,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3668,12 +3670,12 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3698,7 +3700,7 @@
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3708,12 +3710,12 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY15" s="3" t="inlineStr">
@@ -3721,14 +3723,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN006</t>
+          <t>26海安开投MTN002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3738,64 +3738,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683864.IB</t>
+          <t>102683867.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>15.01</v>
+        <v>37.95</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26临空港投MTN004</t>
+          <t>26海安开投MTN001</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+5.00Y</t>
+          <t>1.44Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8338</t>
+          <t>1.5957</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.8000</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司</t>
+          <t>海安开发区建设投资有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.81</t>
+          <t>C- 21.14</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>10-08 14:00</t>
+          <t>10-08 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3819,19 +3819,19 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.23</v>
+        <v>3.6737</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.0</v>
+        <v>1.63</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3842,17 +3842,17 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为10.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
+          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>武汉临空港投资集团有限公司2026年度第六期中期票据</t>
+          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2036-10-09</t>
+          <t>2028-10-09</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3957,12 +3957,14 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN002</t>
+          <t>26宁国建投MTN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3972,7 +3974,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683867.IB</t>
+          <t>102683868.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3981,55 +3983,55 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.5</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9.5</v>
+        <v>10.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>37.95</v>
+        <v>52.95</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26海安开投MTN001</t>
+          <t>26宁国建投MTN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.44Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5957</t>
+          <t>1.8173</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司</t>
+          <t>安徽省宁国建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 21.14</t>
+          <t>C 29.47</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4044,7 +4046,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4053,40 +4055,40 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.6737</v>
+        <v>2.61</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>安徽省-宣城市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额9.5亿元,募集资金用于归还发行人本部存量债务融资工具本金[26海安开投SCP001,24海安开投PPN004,25海安开投CP005,24海安开投PPN005]</t>
+          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海银行股份有限公司</t>
+          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4107,7 +4109,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>海安开发区建设投资有限公司2026年度第二期中期票据</t>
+          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4138,12 +4140,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4198,7 +4200,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26宁国建投MTN002</t>
+          <t>26临空港投MTN005</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4208,121 +4210,121 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683868.IB</t>
+          <t>102683872.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>26临空港投MTN004</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>4.96Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1.8338</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>武汉临空港投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>C+ 34.81</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>10-08 14:00</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V18" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>26宁国建投MTN001</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>1.92Y</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>1.8173</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>安徽省宁国建设投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>C 29.47</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>10-08 09:00</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宣城市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟动态发行,基础发行规模0元,发行金额上限10亿元,拟全部用于偿还发行人存量债务融资工具本金。[26宁国建投CP001,26宁国建投CP002]</t>
+          <t>本期中期票据基础发行规模为0.00亿元,发行金额上限为5.00亿元,募集资金拟全部用于偿还发行人存量债务融资工具的本金[23临空港投MTN003]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,徽商银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4343,7 +4345,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>安徽省宁国建设投资集团有限公司2026年度第二期中期票据</t>
+          <t>武汉临空港投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4353,7 +4355,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-10-09</t>
+          <t>2036-10-09</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4374,12 +4376,12 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
@@ -4404,7 +4406,7 @@
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-10-09</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4414,7 +4416,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4427,9 +4429,7 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
